--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488295_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488295_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.435700000000001</v>
+        <v>9.648099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2168</v>
+        <v>8.207599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.219</v>
+        <v>1.4405</v>
       </c>
       <c r="G2" t="n">
         <v>4.5514</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.301</v>
+        <v>-0.0886</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5656</v>
+        <v>-0.5748</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2646</v>
+        <v>0.4862</v>
       </c>
       <c r="V2" t="n">
         <v>3.1471</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1887</v>
+        <v>6.3977</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4216</v>
+        <v>5.3352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.767</v>
+        <v>1.0625</v>
       </c>
       <c r="G3" t="n">
         <v>0.211</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>0.054</v>
+        <v>0.263</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0621</v>
+        <v>-0.1486</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1161</v>
+        <v>0.4116</v>
       </c>
       <c r="V3" t="n">
         <v>6.2943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2607</v>
+        <v>2.8073</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2009</v>
+        <v>2.3535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0598</v>
+        <v>0.4538</v>
       </c>
       <c r="G4" t="n">
         <v>1.5094</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9162</v>
+        <v>-0.3696</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2014</v>
+        <v>-0.0488</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7148</v>
+        <v>-0.3209</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>A. VIEIRA BARRETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0604</v>
+        <v>0.4483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7462</v>
+        <v>-0.3232</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3142</v>
+        <v>0.7715</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5587</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0561</v>
+        <v>-0.6087</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5026</v>
+        <v>0.0538</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5583</v>
+        <v>-0.0132</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3095</v>
+        <v>-0.159</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2488</v>
+        <v>0.1458</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9997</v>
+        <v>-0.5417</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2534</v>
+        <v>-0.4497</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2537</v>
+        <v>-0.092</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7987</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2647</v>
+        <v>-0.3099</v>
       </c>
       <c r="U6" t="n">
-        <v>1.534</v>
+        <v>0.3867</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0225</v>
+        <v>0.0021</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1359</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1134</v>
+        <v>0.138</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1695</v>
@@ -1000,13 +1000,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4089</v>
+        <v>-0.3843</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.19</v>
+        <v>-0.1654</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VIEIRA BARRETO</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1946</v>
+        <v>-0.5722</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8675</v>
+        <v>-0.2216</v>
       </c>
       <c r="F8" t="n">
-        <v>0.673</v>
+        <v>-0.3506</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5548999999999999</v>
+        <v>1.5587</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6087</v>
+        <v>1.0561</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0538</v>
+        <v>0.5026</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0132</v>
+        <v>2.5583</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.159</v>
+        <v>2.3095</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1458</v>
+        <v>0.2488</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5417</v>
+        <v>-0.9997</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4497</v>
+        <v>-1.2534</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.092</v>
+        <v>0.2537</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5661</v>
+        <v>1.1661</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.2969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2882</v>
+        <v>0.8692</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8392</v>
+        <v>-7.295</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4302</v>
+        <v>-4.5167</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.409</v>
+        <v>-2.7783</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7475</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6292</v>
+        <v>0.1735</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2052</v>
+        <v>-0.2916</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8344</v>
+        <v>0.465</v>
       </c>
       <c r="V10" t="n">
         <v>-4.0915</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.7651</v>
+        <v>11.3122</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4608</v>
+        <v>11.0078</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3044000000000002</v>
+        <v>0.3043999999999998</v>
       </c>
       <c r="G11" t="n">
         <v>5.0321</v>
@@ -1297,7 +1297,7 @@
         <v>-6.2605</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.8348</v>
+        <v>-8.834800000000001</v>
       </c>
       <c r="O11" t="n">
         <v>2.5743</v>
@@ -1312,13 +1312,13 @@
         <v>11.1173</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2113999999999998</v>
+        <v>0.3357999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9522</v>
+        <v>-1.4051</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7408</v>
+        <v>1.7407</v>
       </c>
       <c r="V11" t="n">
         <v>4.0915</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7343</v>
+        <v>2.18</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7331</v>
+        <v>1.9496</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0013</v>
+        <v>0.2303</v>
       </c>
       <c r="G12" t="n">
         <v>0.844</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3378</v>
+        <v>0.7834</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3231</v>
+        <v>0.5397</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0147</v>
+        <v>0.2437</v>
       </c>
       <c r="V12" t="n">
         <v>3.1466</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9824</v>
+        <v>1.6217</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1321</v>
+        <v>1.9362</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1496</v>
+        <v>-0.3145</v>
       </c>
       <c r="G13" t="n">
         <v>2.2038</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9819</v>
+        <v>0.6211</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0684</v>
+        <v>-0.1274</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9135</v>
+        <v>0.7486</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5738</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6343</v>
+        <v>0.2567</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2833</v>
+        <v>0.2063</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.351</v>
+        <v>0.0504</v>
       </c>
       <c r="G14" t="n">
         <v>-0.801</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8889</v>
+        <v>0.0022</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9302</v>
+        <v>-0.4405</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0413</v>
+        <v>0.4427</v>
       </c>
       <c r="V14" t="n">
         <v>0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0833</v>
+        <v>1.0626</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0203</v>
+        <v>-1.0696</v>
       </c>
       <c r="G15" t="n">
         <v>-2.976</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2204</v>
+        <v>-0.2904</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6203</v>
+        <v>-0.641</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3999</v>
+        <v>0.3506</v>
       </c>
       <c r="V15" t="n">
         <v>2.5183</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6658</v>
+        <v>-2.0982</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1231</v>
+        <v>-1.7107</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5427</v>
+        <v>-0.3875</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1663</v>
@@ -1780,13 +1780,13 @@
         <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1681</v>
+        <v>-0.2643</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3756</v>
+        <v>-0.212</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2074</v>
+        <v>-0.0522</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1173</v>
+        <v>-2.4855</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0097</v>
+        <v>-1.2056</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1076</v>
+        <v>-1.2799</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6387</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6685</v>
+        <v>0.3003</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.041</v>
+        <v>-0.2369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7095</v>
+        <v>0.5372</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0899</v>
+        <v>-4.1798</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4143</v>
+        <v>0.2184</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5042</v>
+        <v>-4.3983</v>
       </c>
       <c r="G19" t="n">
         <v>0.4952</v>
@@ -1936,13 +1936,13 @@
         <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3206</v>
+        <v>0.2307</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2873</v>
+        <v>0.0914</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0333</v>
+        <v>0.1393</v>
       </c>
       <c r="V19" t="n">
         <v>-4.7204</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9093</v>
+        <v>-4.2719</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.251</v>
+        <v>-2.7613</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6583</v>
+        <v>-1.5106</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1236</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1562</v>
+        <v>-0.5189</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2037</v>
+        <v>-0.7141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0475</v>
+        <v>0.1952</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.7652</v>
+        <v>-10.1123</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3043000000000005</v>
+        <v>-0.3045</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.4607</v>
+        <v>-9.808000000000002</v>
       </c>
       <c r="G21" t="n">
         <v>-5.032</v>
@@ -2092,13 +2092,13 @@
         <v>9.264299999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2114</v>
+        <v>0.8641</v>
       </c>
       <c r="T21" t="n">
         <v>-1.7408</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9523</v>
+        <v>2.6051</v>
       </c>
       <c r="V21" t="n">
         <v>-4.091599999999999</v>
